--- a/product-definitions/spreadsheet/o3-concentration-profile.xlsx
+++ b/product-definitions/spreadsheet/o3-concentration-profile.xlsx
@@ -1854,7 +1854,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>18</v>
@@ -1866,7 +1866,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
         <v>21</v>
@@ -1878,7 +1878,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
         <v>24</v>
@@ -1890,7 +1890,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="12" t="s">
         <v>38</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
         <v>27</v>
@@ -1914,7 +1914,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="10" t="s">
         <v>40</v>
@@ -1926,7 +1926,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1934,7 +1934,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>42</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
         <v>12</v>
@@ -1956,7 +1956,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9" t="s">
         <v>14</v>
@@ -1968,7 +1968,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="14"/>
       <c r="B31" s="12" t="s">
         <v>2</v>
@@ -1982,7 +1982,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="12" t="s">
         <v>33</v>
@@ -1996,7 +1996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -2008,7 +2008,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="9" t="s">
         <v>16</v>
@@ -2020,7 +2020,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="9" t="s">
         <v>18</v>
@@ -2033,7 +2033,7 @@
       <c r="F35" s="9"/>
       <c r="L35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="9"/>
       <c r="B36" s="9" t="s">
         <v>21</v>
@@ -2046,7 +2046,7 @@
       <c r="F36" s="9"/>
       <c r="L36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="9"/>
       <c r="B37" s="9" t="s">
         <v>24</v>
@@ -2058,7 +2058,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="9"/>
       <c r="B38" s="12" t="s">
         <v>38</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="9"/>
       <c r="B39" s="9" t="s">
         <v>27</v>
@@ -2082,7 +2082,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="9"/>
       <c r="B40" s="10" t="s">
         <v>40</v>
@@ -2094,7 +2094,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="14"/>
@@ -2102,7 +2102,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
         <v>45</v>
       </c>
@@ -2112,7 +2112,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
         <v>12</v>
@@ -2124,7 +2124,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
         <v>14</v>
@@ -2136,7 +2136,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="12"/>
       <c r="B45" s="12" t="s">
         <v>2</v>
@@ -2148,7 +2148,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
         <v>16</v>
@@ -2172,7 +2172,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
         <v>18</v>
@@ -2184,7 +2184,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="9"/>
       <c r="B49" s="9" t="s">
         <v>21</v>
@@ -2196,7 +2196,7 @@
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="9"/>
       <c r="B50" s="9" t="s">
         <v>24</v>
@@ -2208,7 +2208,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="9"/>
       <c r="B51" s="12" t="s">
         <v>38</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="9"/>
       <c r="B52" s="9" t="s">
         <v>27</v>
@@ -2232,7 +2232,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="9"/>
       <c r="B53" s="10" t="s">
         <v>40</v>
@@ -2244,7 +2244,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2252,7 +2252,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="21" t="s">
         <v>48</v>
       </c>
@@ -2262,7 +2262,7 @@
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="9"/>
       <c r="B56" s="9" t="s">
         <v>12</v>
@@ -2274,7 +2274,7 @@
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="9"/>
       <c r="B57" s="9" t="s">
         <v>14</v>
@@ -2286,7 +2286,7 @@
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="12"/>
       <c r="B58" s="12" t="s">
         <v>2</v>
@@ -2298,7 +2298,7 @@
       <c r="E58" s="14"/>
       <c r="F58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="9"/>
       <c r="B59" s="9" t="s">
         <v>15</v>
@@ -2310,7 +2310,7 @@
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9"/>
       <c r="B60" s="9" t="s">
         <v>16</v>
@@ -2322,7 +2322,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="9"/>
       <c r="B61" s="9" t="s">
         <v>18</v>
@@ -2334,7 +2334,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="9"/>
       <c r="B62" s="9" t="s">
         <v>21</v>
@@ -2346,7 +2346,7 @@
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="9"/>
       <c r="B63" s="9" t="s">
         <v>24</v>
@@ -2358,7 +2358,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="9"/>
       <c r="B64" s="12" t="s">
         <v>38</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="9"/>
       <c r="B65" s="9" t="s">
         <v>27</v>
@@ -2382,7 +2382,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
         <v>40</v>
@@ -2394,14 +2394,15 @@
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
     </row>
-    <row r="68">
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
         <v>52</v>
@@ -2410,7 +2411,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>12</v>
@@ -2419,7 +2420,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
         <v>14</v>
@@ -2428,7 +2429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
         <v>2</v>
@@ -2437,14 +2438,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="6"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -2453,7 +2454,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="9" t="s">
         <v>56</v>
@@ -2463,7 +2464,7 @@
       </c>
       <c r="D75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="14" t="s">
         <v>58</v>
@@ -2514,7 +2515,7 @@
       <c r="B85" s="9"/>
       <c r="C85" s="12"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="14"/>
       <c r="C86" s="20"/>
